--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-wgisd_small.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-wgisd_small.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>124.4577260017395</v>
+        <v>231.4211993217468</v>
       </c>
       <c r="D2" t="n">
-        <v>6.53000020980835</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2099611111103542</v>
+        <v>0.5184708510126387</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6265060305595398</v>
+        <v>0.7142857313156128</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4057480990886688</v>
+        <v>0.4343037009239197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4040574729442596</v>
+        <v>0.4264214038848877</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4159592390060425</v>
+        <v>0.4280936419963836</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1066460311412811</v>
+        <v>0.1885083019733429</v>
       </c>
       <c r="K2" t="n">
-        <v>29.18390607833862</v>
+        <v>124.4063413143158</v>
       </c>
       <c r="L2" t="n">
-        <v>0.077248469988505</v>
+        <v>0.1342202345530192</v>
       </c>
       <c r="M2" t="n">
-        <v>0.151334015528361</v>
+        <v>0.5751121520996094</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1957474152247111</v>
+        <v>0.2800420920054118</v>
       </c>
       <c r="O2" t="n">
-        <v>2.317454099655152</v>
+        <v>4.026607036590576</v>
       </c>
       <c r="P2" t="n">
-        <v>4.54002046585083</v>
+        <v>17.25336456298828</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.872422456741333</v>
+        <v>8.401262760162354</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-162249</t>
+          <t>20250725-231454</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>84.61009502410889</v>
+        <v>205.1159963607788</v>
       </c>
       <c r="D3" t="n">
-        <v>6.53000020980835</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2029099772835886</v>
+        <v>0.5152245875327818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5450901985168457</v>
+        <v>0.7118644118309021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3907666802406311</v>
+        <v>0.4546197950839996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.393415629863739</v>
+        <v>0.447635143995285</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3939899802207947</v>
+        <v>0.4467005133628845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0994007140398025</v>
+        <v>0.1753601878881454</v>
       </c>
       <c r="K3" t="n">
-        <v>29.46430850028992</v>
+        <v>128.944326877594</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0757128636042277</v>
+        <v>0.135486102104187</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1496650218963623</v>
+        <v>0.5732309182484945</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1941637198130289</v>
+        <v>0.2802748123804728</v>
       </c>
       <c r="O3" t="n">
-        <v>2.271385908126831</v>
+        <v>4.06458306312561</v>
       </c>
       <c r="P3" t="n">
-        <v>4.489950656890869</v>
+        <v>17.19692754745483</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.824911594390869</v>
+        <v>8.408244371414185</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-162606</t>
+          <t>20250725-232211</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>91.76186800003052</v>
+        <v>207.0878319740296</v>
       </c>
       <c r="D4" t="n">
-        <v>6.599999904632568</v>
+        <v>15.63000011444092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2024087623712864</v>
+        <v>0.5161795250831112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5902438759803772</v>
+        <v>0.6681128144264221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3790322542190552</v>
+        <v>0.4398625493049621</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3784692883491516</v>
+        <v>0.4397537410259247</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3696202635765075</v>
+        <v>0.432043194770813</v>
       </c>
       <c r="J4" t="n">
-        <v>0.097963809967041</v>
+        <v>0.1794710010290146</v>
       </c>
       <c r="K4" t="n">
-        <v>29.36896204948425</v>
+        <v>119.4540474414825</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07467085520426429</v>
+        <v>0.1323601166407267</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1487170775731404</v>
+        <v>0.562483008702596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1735356092453003</v>
+        <v>0.2787638505299886</v>
       </c>
       <c r="O4" t="n">
-        <v>2.24012565612793</v>
+        <v>3.970803499221802</v>
       </c>
       <c r="P4" t="n">
-        <v>4.461512327194214</v>
+        <v>16.87449026107788</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.206068277359009</v>
+        <v>8.362915515899658</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-162844</t>
+          <t>20250725-232856</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>86.65130639076233</v>
+        <v>255.4834952354431</v>
       </c>
       <c r="D5" t="n">
-        <v>6.53000020980835</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2146787369667097</v>
+        <v>0.5157060118821951</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6091127395629883</v>
+        <v>0.7512437701225281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3996641337871551</v>
+        <v>0.4631043374538421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3935309946537018</v>
+        <v>0.4556521773338318</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3871559500694275</v>
+        <v>0.4565972089767456</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08841155469417571</v>
+        <v>0.1798423081636428</v>
       </c>
       <c r="K5" t="n">
-        <v>29.27169227600098</v>
+        <v>131.3412034511566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0735185702641805</v>
+        <v>0.1334469556808471</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1473366419474283</v>
+        <v>0.5575254519780477</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1715156952540079</v>
+        <v>0.2805980682373047</v>
       </c>
       <c r="O5" t="n">
-        <v>2.205557107925415</v>
+        <v>4.003408670425415</v>
       </c>
       <c r="P5" t="n">
-        <v>4.420099258422852</v>
+        <v>16.72576355934143</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.145470857620239</v>
+        <v>8.417942047119141</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-163138</t>
+          <t>20250725-233539</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>140.0147500038147</v>
+        <v>231.5283050537109</v>
       </c>
       <c r="D6" t="n">
-        <v>6.53000020980835</v>
+        <v>15.57999992370606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2115021398369695</v>
+        <v>0.5172721368925912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6430379748344421</v>
+        <v>0.7326732873916626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4233226776123047</v>
+        <v>0.4490861594676971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3996478915214538</v>
+        <v>0.4501278698444366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3946902751922607</v>
+        <v>0.4419213831424713</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1002362444996833</v>
+        <v>0.1815132647752761</v>
       </c>
       <c r="K6" t="n">
-        <v>28.92077803611756</v>
+        <v>120.9316499233246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0731848319371541</v>
+        <v>0.134320855140686</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1508809010187785</v>
+        <v>0.5637182633082072</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2088205893834432</v>
+        <v>0.2774632692337036</v>
       </c>
       <c r="O6" t="n">
-        <v>2.195544958114624</v>
+        <v>4.029625654220581</v>
       </c>
       <c r="P6" t="n">
-        <v>4.526427030563354</v>
+        <v>16.91154789924622</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.264617681503296</v>
+        <v>8.323898077011108</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-163427</t>
+          <t>20250725-234322</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>142.6133725643158</v>
+        <v>638.8709628582001</v>
       </c>
       <c r="D2" t="n">
-        <v>9.779999732971191</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3152470165683377</v>
+        <v>0.6388416158802369</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7196030020713806</v>
+        <v>0.7435897588729858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4409991502761841</v>
+        <v>0.3505696654319763</v>
       </c>
       <c r="H2" t="n">
-        <v>0.437609851360321</v>
+        <v>0.359020859003067</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4364292025566101</v>
+        <v>0.343777984380722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1243936195969581</v>
+        <v>0.1766319572925567</v>
       </c>
       <c r="K2" t="n">
-        <v>131.2245399951935</v>
+        <v>191.6877057552338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1517134348551432</v>
+        <v>0.1767347892125447</v>
       </c>
       <c r="M2" t="n">
-        <v>0.56041472752889</v>
+        <v>0.3135081529617309</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2668010234832764</v>
+        <v>0.3446598132451375</v>
       </c>
       <c r="O2" t="n">
-        <v>4.551403045654297</v>
+        <v>5.302043676376343</v>
       </c>
       <c r="P2" t="n">
-        <v>16.8124418258667</v>
+        <v>9.405244588851929</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.004030704498291</v>
+        <v>10.33979439735413</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-064431</t>
+          <t>20250724-171031</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>155.428991317749</v>
+        <v>628.9838078022003</v>
       </c>
       <c r="D3" t="n">
-        <v>9.779999732971191</v>
+        <v>20.46999931335449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3131234696933201</v>
+        <v>0.6451561243245096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7431421279907227</v>
+        <v>0.6252983212471008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4534004926681518</v>
+        <v>0.4438596367835998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.450963944196701</v>
+        <v>0.4397537410259247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4500419795513153</v>
+        <v>0.4462222158908844</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1193831637501716</v>
+        <v>0.1445315778255462</v>
       </c>
       <c r="K3" t="n">
-        <v>127.6323039531708</v>
+        <v>185.9119479656219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1478962818781534</v>
+        <v>0.1462043126424153</v>
       </c>
       <c r="M3" t="n">
-        <v>0.57943700949351</v>
+        <v>0.3042511542638142</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2884536981582641</v>
+        <v>0.3589737812678019</v>
       </c>
       <c r="O3" t="n">
-        <v>4.436888456344604</v>
+        <v>4.386129379272461</v>
       </c>
       <c r="P3" t="n">
-        <v>17.3831102848053</v>
+        <v>9.127534627914429</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.653610944747925</v>
+        <v>10.76921343803406</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-065033</t>
+          <t>20250724-172553</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>141.3804161548615</v>
+        <v>414.1806712150574</v>
       </c>
       <c r="D4" t="n">
-        <v>9.960000038146973</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3143398800203877</v>
+        <v>0.6404979626337687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7038834691047668</v>
+        <v>0.63922518491745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.3623445928096771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.3620230555534363</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.3671232759952545</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1239888221025466</v>
+        <v>0.1425846368074417</v>
       </c>
       <c r="K4" t="n">
-        <v>129.2937817573547</v>
+        <v>192.1790301799774</v>
       </c>
       <c r="L4" t="n">
-        <v>0.150047222773234</v>
+        <v>0.1641009410222371</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5893449624379475</v>
+        <v>0.3177040179570516</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2870042403539022</v>
+        <v>0.3538630723953247</v>
       </c>
       <c r="O4" t="n">
-        <v>4.501416683197021</v>
+        <v>4.923028230667114</v>
       </c>
       <c r="P4" t="n">
-        <v>17.68034887313843</v>
+        <v>9.531120538711548</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.610127210617065</v>
+        <v>10.61589217185974</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-065628</t>
+          <t>20250724-174055</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4046,53 +4046,53 @@
         <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>209.8801534175873</v>
+        <v>456.1517362594605</v>
       </c>
       <c r="D5" t="n">
-        <v>9.890000343322754</v>
+        <v>20.46999931335449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3148489626164132</v>
+        <v>0.6394331937140607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.748129665851593</v>
+        <v>0.6186046600341797</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4762726426124573</v>
+        <v>0.2939758896827698</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4750430285930633</v>
+        <v>0.290996789932251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4726027250289917</v>
+        <v>0.2783688008785248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1239183619618415</v>
+        <v>0.1468205004930496</v>
       </c>
       <c r="K5" t="n">
-        <v>133.7193670272827</v>
+        <v>192.1340489387512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1539128383000691</v>
+        <v>0.1456385374069214</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5809991200764973</v>
+        <v>0.3023016770680745</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2854173024495443</v>
+        <v>0.3625367879867553</v>
       </c>
       <c r="O5" t="n">
-        <v>4.617385149002075</v>
+        <v>4.369156122207642</v>
       </c>
       <c r="P5" t="n">
-        <v>17.42997360229492</v>
+        <v>9.069050312042236</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.562519073486328</v>
+        <v>10.87610363960266</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-070223</t>
+          <t>20250724-175223</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>123.7307920455933</v>
+        <v>397.8733375072479</v>
       </c>
       <c r="D6" t="n">
-        <v>9.770000457763672</v>
+        <v>22.36000061035156</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3135229371212147</v>
+        <v>0.6328373609519586</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7124010324478149</v>
+        <v>0.5673758983612061</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4112903177738189</v>
+        <v>0.2622686922550201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4071550369262695</v>
+        <v>0.2364444434642791</v>
       </c>
       <c r="I6" t="n">
-        <v>0.40686696767807</v>
+        <v>0.2581211626529693</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1207424327731132</v>
+        <v>0.1564124226570129</v>
       </c>
       <c r="K6" t="n">
-        <v>135.0488703250885</v>
+        <v>186.1560394763947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.144041887919108</v>
+        <v>0.1550127744674682</v>
       </c>
       <c r="M6" t="n">
-        <v>0.566878342628479</v>
+        <v>0.3001683950424194</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2882202625274658</v>
+        <v>0.3522663434346517</v>
       </c>
       <c r="O6" t="n">
-        <v>4.321256637573242</v>
+        <v>4.650383234024048</v>
       </c>
       <c r="P6" t="n">
-        <v>17.00635027885437</v>
+        <v>9.005051851272583</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.646607875823975</v>
+        <v>10.56799030303955</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-070930</t>
+          <t>20250724-180433</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>304.4573345184326</v>
+        <v>304.620626449585</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25</v>
+        <v>10.68000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6021689339991538</v>
+        <v>0.4112415658310056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5490196347236633</v>
+        <v>0.5707656741142273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.296875</v>
+        <v>0.2993799746036529</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2844827473163605</v>
+        <v>0.2981366515159607</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2673611044883728</v>
+        <v>0.3174030780792236</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1327849924564361</v>
+        <v>0.155021846294403</v>
       </c>
       <c r="K2" t="n">
-        <v>193.849490404129</v>
+        <v>88.80021786689758</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1728531281153361</v>
+        <v>0.1768564462661743</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3002717971801757</v>
+        <v>0.3197389523188273</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3598780870437622</v>
+        <v>0.2979832331339518</v>
       </c>
       <c r="O2" t="n">
-        <v>5.185593843460083</v>
+        <v>5.305693387985229</v>
       </c>
       <c r="P2" t="n">
-        <v>9.008153915405272</v>
+        <v>9.592168569564819</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.79634261131287</v>
+        <v>8.939496994018555</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-135952</t>
+          <t>20250727-021648</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>286.8989062309265</v>
+        <v>355.6270399093628</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5600004196167</v>
+        <v>10.64000034332275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6044797866508879</v>
+        <v>0.4296530893870762</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5195402503013611</v>
+        <v>0.5785536170005798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2544769048690796</v>
+        <v>0.3089840412139892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2546749711036682</v>
+        <v>0.2994652390480041</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2451154589653015</v>
+        <v>0.3172541856765747</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1413804143667221</v>
+        <v>0.1531938165426254</v>
       </c>
       <c r="K3" t="n">
-        <v>202.5709321498871</v>
+        <v>90.96725606918336</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1639691352844238</v>
+        <v>0.1646188020706177</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3101998567581177</v>
+        <v>0.3192956368128458</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3368341207504272</v>
+        <v>0.2990791320800781</v>
       </c>
       <c r="O3" t="n">
-        <v>4.919074058532715</v>
+        <v>4.93856406211853</v>
       </c>
       <c r="P3" t="n">
-        <v>9.30599570274353</v>
+        <v>9.578869104385376</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.10502362251282</v>
+        <v>8.972373962402344</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-140932</t>
+          <t>20250727-022455</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>284.2404017448425</v>
+        <v>370.3886153697968</v>
       </c>
       <c r="D4" t="n">
-        <v>13.98999977111816</v>
+        <v>10.78999996185303</v>
       </c>
       <c r="E4" t="n">
-        <v>0.60569000141374</v>
+        <v>0.4355367188518111</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4878048896789551</v>
+        <v>0.5373831987380981</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2154605239629745</v>
+        <v>0.3240823745727539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2163153141736984</v>
+        <v>0.350649356842041</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1929026395082473</v>
+        <v>0.3233215510845184</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1299525201320648</v>
+        <v>0.1474709659814834</v>
       </c>
       <c r="K4" t="n">
-        <v>201.8468110561371</v>
+        <v>80.60772061347961</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1619638125101725</v>
+        <v>0.1675407091776529</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3190139214197794</v>
+        <v>0.3197187662124633</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3622663100560506</v>
+        <v>0.3014747301737467</v>
       </c>
       <c r="O4" t="n">
-        <v>4.858914375305176</v>
+        <v>5.02622127532959</v>
       </c>
       <c r="P4" t="n">
-        <v>9.570417642593384</v>
+        <v>9.5915629863739</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.86798930168152</v>
+        <v>9.044241905212402</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-141914</t>
+          <t>20250727-023354</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>299.4941368103027</v>
+        <v>358.1886749267578</v>
       </c>
       <c r="D5" t="n">
-        <v>14.07999992370606</v>
+        <v>10.68000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6122981826464335</v>
+        <v>0.431484075056182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5027322173118591</v>
+        <v>0.5760368704795837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3382737636566162</v>
+        <v>0.3586083948612213</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3342516124248504</v>
+        <v>0.3409669101238251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3189734220504761</v>
+        <v>0.3367697596549988</v>
       </c>
       <c r="J5" t="n">
-        <v>0.137833371758461</v>
+        <v>0.1627134829759597</v>
       </c>
       <c r="K5" t="n">
-        <v>208.4463844299316</v>
+        <v>88.96827793121338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1713857889175415</v>
+        <v>0.1596646865208943</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3147690693537394</v>
+        <v>0.3293690681457519</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3512994527816772</v>
+        <v>0.2961112340291341</v>
       </c>
       <c r="O5" t="n">
-        <v>5.141573667526245</v>
+        <v>4.789940595626831</v>
       </c>
       <c r="P5" t="n">
-        <v>9.443072080612184</v>
+        <v>9.88107204437256</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.53898358345032</v>
+        <v>8.883337020874023</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-142844</t>
+          <t>20250727-024259</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>286.5747759342194</v>
+        <v>307.9846019744873</v>
       </c>
       <c r="D6" t="n">
-        <v>13.97999954223633</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5952669032688799</v>
+        <v>0.4115945668891072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6004140973091125</v>
+        <v>0.5176470875740051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2622456550598144</v>
+        <v>0.3378256857395172</v>
       </c>
       <c r="H6" t="n">
-        <v>0.226962462067604</v>
+        <v>0.3294538855552673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2364106923341751</v>
+        <v>0.3382225930690765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.137919008731842</v>
+        <v>0.1482863426208496</v>
       </c>
       <c r="K6" t="n">
-        <v>198.3032715320587</v>
+        <v>83.98106074333191</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1565481503804524</v>
+        <v>0.1621167262395223</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3054827213287353</v>
+        <v>0.317872675259908</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3554211298624674</v>
+        <v>0.3002293268839518</v>
       </c>
       <c r="O6" t="n">
-        <v>4.696444511413574</v>
+        <v>4.863501787185669</v>
       </c>
       <c r="P6" t="n">
-        <v>9.164481639862061</v>
+        <v>9.536180257797239</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.66263389587402</v>
+        <v>9.006879806518555</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-143845</t>
+          <t>20250727-025153</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>221.8238356113434</v>
+        <v>340.4036734104156</v>
       </c>
       <c r="D2" t="n">
-        <v>9.560000419616699</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4396727340562003</v>
+        <v>0.3800288767230754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4215456545352936</v>
+        <v>0.4646017551422119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2010050266981125</v>
+        <v>0.2448630183935165</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1956911981105804</v>
+        <v>0.2527675330638885</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2120075076818466</v>
+        <v>0.0755467191338539</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1378657966852188</v>
+        <v>0.118205152451992</v>
       </c>
       <c r="K2" t="n">
-        <v>93.78946208953856</v>
+        <v>35.30588245391846</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1785492658615112</v>
+        <v>0.1351346492767334</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3166065375010172</v>
+        <v>0.1761168718338012</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2978625933329264</v>
+        <v>0.1956769545873006</v>
       </c>
       <c r="O2" t="n">
-        <v>5.356477975845337</v>
+        <v>4.054039478302002</v>
       </c>
       <c r="P2" t="n">
-        <v>9.498196125030518</v>
+        <v>5.283506155014038</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.935877799987793</v>
+        <v>5.870308637619019</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-032537</t>
+          <t>20250728-054520</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>204.6332259178162</v>
+        <v>334.357569694519</v>
       </c>
       <c r="D3" t="n">
-        <v>9.819999694824221</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4292373782710025</v>
+        <v>0.3869869901488225</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5308057069778442</v>
+        <v>0.443418025970459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2590975165367126</v>
+        <v>0.2751407921314239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2389380484819412</v>
+        <v>0.2718120813369751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2414746582508087</v>
+        <v>0.2811979949474334</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1388741880655288</v>
+        <v>0.0992135852575302</v>
       </c>
       <c r="K3" t="n">
-        <v>94.39130401611328</v>
+        <v>29.96552681922913</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1723148187001546</v>
+        <v>0.1192088445027669</v>
       </c>
       <c r="M3" t="n">
-        <v>0.316466490427653</v>
+        <v>0.1616299629211425</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2959670225779215</v>
+        <v>0.2030985196431478</v>
       </c>
       <c r="O3" t="n">
-        <v>5.169444561004639</v>
+        <v>3.576265335083008</v>
       </c>
       <c r="P3" t="n">
-        <v>9.49399471282959</v>
+        <v>4.848898887634277</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.879010677337646</v>
+        <v>6.092955589294434</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-033221</t>
+          <t>20250728-055236</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>197.2862439155578</v>
+        <v>381.0105175971985</v>
       </c>
       <c r="D4" t="n">
-        <v>9.970000267028809</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4184494191094449</v>
+        <v>0.3863584821874445</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3783783912658691</v>
+        <v>0.4395604431629181</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1824440658092498</v>
+        <v>0.294117659330368</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1882542222738266</v>
+        <v>0.2882562279701233</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1567346900701522</v>
+        <v>0.2783945202827453</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1379759758710861</v>
+        <v>0.1058574989438057</v>
       </c>
       <c r="K4" t="n">
-        <v>91.659259557724</v>
+        <v>35.79855394363403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1734849214553833</v>
+        <v>0.1221308628718058</v>
       </c>
       <c r="M4" t="n">
-        <v>0.320215106010437</v>
+        <v>0.167853291829427</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3161356528600057</v>
+        <v>0.1841389258702596</v>
       </c>
       <c r="O4" t="n">
-        <v>5.204547643661499</v>
+        <v>3.663925886154175</v>
       </c>
       <c r="P4" t="n">
-        <v>9.60645318031311</v>
+        <v>5.035598754882812</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.484069585800173</v>
+        <v>5.524167776107788</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-033848</t>
+          <t>20250728-055936</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>201.8870024681092</v>
+        <v>296.5318441390991</v>
       </c>
       <c r="D5" t="n">
-        <v>9.939999580383301</v>
+        <v>5.480000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4216804723990591</v>
+        <v>0.3903203003463291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5109170079231262</v>
+        <v>0.3674321472644806</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2546419203281402</v>
+        <v>0.2833471298217773</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2474418580532074</v>
+        <v>0.2841269969940185</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2397072315216064</v>
+        <v>0.1423001885414123</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1465998142957687</v>
+        <v>0.1023236736655235</v>
       </c>
       <c r="K5" t="n">
-        <v>91.32409000396729</v>
+        <v>34.80442094802856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1835981051127116</v>
+        <v>0.1276658693949381</v>
       </c>
       <c r="M5" t="n">
-        <v>0.319897985458374</v>
+        <v>0.1653822501500447</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3006495714187622</v>
+        <v>0.1728669007619222</v>
       </c>
       <c r="O5" t="n">
-        <v>5.507943153381348</v>
+        <v>3.829976081848145</v>
       </c>
       <c r="P5" t="n">
-        <v>9.596939563751221</v>
+        <v>4.961467504501343</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.019487142562866</v>
+        <v>5.186007022857666</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-034506</t>
+          <t>20250728-060732</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>205.835845708847</v>
+        <v>327.6742877960205</v>
       </c>
       <c r="D6" t="n">
-        <v>9.390000343322754</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4279025212714546</v>
+        <v>0.3903480362384877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4035476744174957</v>
+        <v>0.3860369622707367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2476190477609634</v>
+        <v>0.1856392323970794</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2409012168645858</v>
+        <v>0.1918047070503235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2404274195432663</v>
+        <v>0.0537634417414665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1376744657754898</v>
+        <v>0.1092731654644012</v>
       </c>
       <c r="K6" t="n">
-        <v>94.64475250244141</v>
+        <v>35.53262877464294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1765918811162312</v>
+        <v>0.1142449696858724</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3185456355412801</v>
+        <v>0.1588007767995198</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2965879758199056</v>
+        <v>0.1849426666895548</v>
       </c>
       <c r="O6" t="n">
-        <v>5.297756433486938</v>
+        <v>3.427349090576172</v>
       </c>
       <c r="P6" t="n">
-        <v>9.556369066238403</v>
+        <v>4.764023303985596</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.897639274597168</v>
+        <v>5.548280000686646</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-035128</t>
+          <t>20250728-061403</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>141.3664801120758</v>
+        <v>270.5547842979431</v>
       </c>
       <c r="D2" t="n">
-        <v>3.319999933242798</v>
+        <v>7.389999866485596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3927778131083438</v>
+        <v>0.4238420631736517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2804878056049347</v>
+        <v>0.4924623072147369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1102204397320747</v>
+        <v>0.3330300152301788</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1000000014901161</v>
+        <v>0.3096309602260589</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1015560999512672</v>
+        <v>0.3318223059177398</v>
       </c>
       <c r="J2" t="n">
-        <v>0.102298304438591</v>
+        <v>0.1400473117828369</v>
       </c>
       <c r="K2" t="n">
-        <v>38.23464798927307</v>
+        <v>58.99226236343384</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1219939549763997</v>
+        <v>0.1449503183364868</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1652129252751668</v>
+        <v>0.2334705352783203</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1835928916931152</v>
+        <v>0.2819442272186279</v>
       </c>
       <c r="O2" t="n">
-        <v>3.659818649291992</v>
+        <v>4.348509550094604</v>
       </c>
       <c r="P2" t="n">
-        <v>4.956387758255005</v>
+        <v>7.004116058349609</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.507786750793457</v>
+        <v>8.458326816558838</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-174709</t>
+          <t>20250729-092658</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>145.6159021854401</v>
+        <v>240.0836265087128</v>
       </c>
       <c r="D3" t="n">
-        <v>3.210000038146973</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3999897225906974</v>
+        <v>0.4189797228780286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3468950688838959</v>
+        <v>0.5303030014038086</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1438202261924743</v>
+        <v>0.3569793999195099</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1301482766866684</v>
+        <v>0.3548386991024017</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1202370896935463</v>
+        <v>0.3216080367565155</v>
       </c>
       <c r="J3" t="n">
-        <v>0.110036201775074</v>
+        <v>0.1367764770984649</v>
       </c>
       <c r="K3" t="n">
-        <v>38.99452996253967</v>
+        <v>59.6532678604126</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1156622012456258</v>
+        <v>0.1326443751653035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1583548784255981</v>
+        <v>0.2247185230255127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1872025569279988</v>
+        <v>0.2726546049118042</v>
       </c>
       <c r="O3" t="n">
-        <v>3.469866037368774</v>
+        <v>3.979331254959106</v>
       </c>
       <c r="P3" t="n">
-        <v>4.750646352767944</v>
+        <v>6.741555690765381</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.616076707839966</v>
+        <v>8.179638147354126</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-175108</t>
+          <t>20250729-093331</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>140.0060107707977</v>
+        <v>270.8848686218262</v>
       </c>
       <c r="D4" t="n">
-        <v>3.059999942779541</v>
+        <v>8.090000152587891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3943055993632266</v>
+        <v>0.3921202876988579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2915810942649841</v>
+        <v>0.5253456234931946</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1002892926335334</v>
+        <v>0.3680672347545624</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1011058464646339</v>
+        <v>0.3798319399356842</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0951541885733604</v>
+        <v>0.3834196925163269</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1283047944307327</v>
+        <v>0.120436318218708</v>
       </c>
       <c r="K4" t="n">
-        <v>44.01828241348267</v>
+        <v>53.13425779342651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1155351320902506</v>
+        <v>0.133258040746053</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1583154598871866</v>
+        <v>0.2306999683380127</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1907527844111124</v>
+        <v>0.2685616413752238</v>
       </c>
       <c r="O4" t="n">
-        <v>3.46605396270752</v>
+        <v>3.997741222381592</v>
       </c>
       <c r="P4" t="n">
-        <v>4.749463796615601</v>
+        <v>6.920999050140381</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.722583532333374</v>
+        <v>8.056849241256714</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-175512</t>
+          <t>20250729-093933</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>144.2353496551514</v>
+        <v>433.461373090744</v>
       </c>
       <c r="D5" t="n">
-        <v>3.180000066757202</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4124418622569034</v>
+        <v>0.4017352557608059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1791044771671295</v>
+        <v>0.5342789888381958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0290979631245136</v>
+        <v>0.4217804670333862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01970443315804</v>
+        <v>0.423922598361969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0540000014007091</v>
+        <v>0.4023870527744293</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1087466850876808</v>
+        <v>0.1469431668519973</v>
       </c>
       <c r="K5" t="n">
-        <v>37.45798707008362</v>
+        <v>52.71495151519776</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1083664973576863</v>
+        <v>0.1337629318237304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1581088066101074</v>
+        <v>0.246334687868754</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1992878675460815</v>
+        <v>0.2701084693272909</v>
       </c>
       <c r="O5" t="n">
-        <v>3.250994920730591</v>
+        <v>4.012887954711914</v>
       </c>
       <c r="P5" t="n">
-        <v>4.743264198303223</v>
+        <v>7.390040636062622</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.978636026382446</v>
+        <v>8.103254079818726</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-175916</t>
+          <t>20250729-094616</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>146.2894251346588</v>
+        <v>234.1296572685242</v>
       </c>
       <c r="D6" t="n">
-        <v>3.210000038146973</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4084589136274237</v>
+        <v>0.3929489922934565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2588996887207031</v>
+        <v>0.447826087474823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0714285746216774</v>
+        <v>0.2708333432674408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0729366615414619</v>
+        <v>0.2569738030433655</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0949913635849952</v>
+        <v>0.2402088791131973</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1024803444743156</v>
+        <v>0.133770540356636</v>
       </c>
       <c r="K6" t="n">
-        <v>36.08000183105469</v>
+        <v>58.83769154548645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1197610696156819</v>
+        <v>0.1316856861114502</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1630369186401367</v>
+        <v>0.2283588329950968</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1822854439417521</v>
+        <v>0.258989405632019</v>
       </c>
       <c r="O6" t="n">
-        <v>3.592832088470459</v>
+        <v>3.950570583343506</v>
       </c>
       <c r="P6" t="n">
-        <v>4.891107559204102</v>
+        <v>6.850764989852905</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.468563318252564</v>
+        <v>7.769682168960571</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-180317</t>
+          <t>20250729-095536</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C2" t="n">
-        <v>176.3456213474274</v>
+        <v>209.6861126422882</v>
       </c>
       <c r="D2" t="n">
-        <v>6.639999866485596</v>
+        <v>10.47000026702881</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3928473378930773</v>
+        <v>0.3333360829823453</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4267782568931579</v>
+        <v>0.5584725737571716</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2413470596075058</v>
+        <v>0.3219954669475555</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2367066890001297</v>
+        <v>0.3034367263317108</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2174688130617141</v>
+        <v>0.3010033369064331</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1308690458536148</v>
+        <v>0.08718427270650859</v>
       </c>
       <c r="K2" t="n">
-        <v>54.21937227249146</v>
+        <v>22.05118608474731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1399775664011637</v>
+        <v>0.0620630264282226</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2343187014261881</v>
+        <v>0.1160976409912109</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2722110112508138</v>
+        <v>0.1213075081507364</v>
       </c>
       <c r="O2" t="n">
-        <v>4.199326992034912</v>
+        <v>1.86189079284668</v>
       </c>
       <c r="P2" t="n">
-        <v>7.029561042785645</v>
+        <v>3.482929229736328</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.166330337524414</v>
+        <v>3.639225244522095</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-060455</t>
+          <t>20250730-091729</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>160.4203128814697</v>
+        <v>378.9936556816101</v>
       </c>
       <c r="D3" t="n">
-        <v>6.769999980926514</v>
+        <v>10.48999977111816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3956835787547262</v>
+        <v>0.3212321798006693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3991507291793823</v>
+        <v>0.4956521689891815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1819757372140884</v>
+        <v>0.3893376290798187</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1791320443153381</v>
+        <v>0.3925686478614807</v>
       </c>
       <c r="I3" t="n">
-        <v>0.183803454041481</v>
+        <v>0.3777239620685577</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1353623121976852</v>
+        <v>0.0873652473092079</v>
       </c>
       <c r="K3" t="n">
-        <v>62.84681296348572</v>
+        <v>16.20252776145935</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1598133166631062</v>
+        <v>0.0667441129684448</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2367019414901733</v>
+        <v>0.1241779168446858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2760711034138997</v>
+        <v>0.1377917289733886</v>
       </c>
       <c r="O3" t="n">
-        <v>4.794399499893188</v>
+        <v>2.002323389053345</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1010582447052</v>
+        <v>3.725337505340576</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.282133102416992</v>
+        <v>4.13375186920166</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-061007</t>
+          <t>20250730-092205</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>162.0132014751434</v>
+        <v>231.5119004249573</v>
       </c>
       <c r="D4" t="n">
-        <v>7.070000171661377</v>
+        <v>10.48999977111816</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3962995896213933</v>
+        <v>0.3323237514948543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5224839448928833</v>
+        <v>0.5034013390541077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2336227297782898</v>
+        <v>0.3597561120986938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2380952388048172</v>
+        <v>0.3602058291435241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2549870014190674</v>
+        <v>0.351548284292221</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1107792854309082</v>
+        <v>0.08967488259077069</v>
       </c>
       <c r="K4" t="n">
-        <v>60.75086283683777</v>
+        <v>21.75267887115479</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1553667147954305</v>
+        <v>0.0668294827143351</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2293653170267741</v>
+        <v>0.1210077921549479</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2660517454147338</v>
+        <v>0.1252235412597656</v>
       </c>
       <c r="O4" t="n">
-        <v>4.661001443862915</v>
+        <v>2.004884481430054</v>
       </c>
       <c r="P4" t="n">
-        <v>6.880959510803223</v>
+        <v>3.630233764648438</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.981552362442017</v>
+        <v>3.756706237792969</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-061454</t>
+          <t>20250730-092932</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="C5" t="n">
-        <v>162.5973572731018</v>
+        <v>304.1610200405121</v>
       </c>
       <c r="D5" t="n">
-        <v>6.869999885559082</v>
+        <v>10.53999996185303</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4066678175800725</v>
+        <v>0.3345241115509885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4708737730979919</v>
+        <v>0.483739823102951</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2891986072063446</v>
+        <v>0.3815126121044159</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2956204414367676</v>
+        <v>0.3795130252838135</v>
       </c>
       <c r="I5" t="n">
-        <v>0.267234057188034</v>
+        <v>0.3729372918605804</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1362102478742599</v>
+        <v>0.08584489673376081</v>
       </c>
       <c r="K5" t="n">
-        <v>63.15753221511841</v>
+        <v>21.83402967453003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1609100818634033</v>
+        <v>0.0664751688639322</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2315889437993367</v>
+        <v>0.1205152908960978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2855231523513794</v>
+        <v>0.1255152781804402</v>
       </c>
       <c r="O5" t="n">
-        <v>4.8273024559021</v>
+        <v>1.994255065917969</v>
       </c>
       <c r="P5" t="n">
-        <v>6.947668313980103</v>
+        <v>3.615458726882935</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.565694570541382</v>
+        <v>3.765458345413208</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-061952</t>
+          <t>20250730-093430</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>163.9413049221039</v>
+        <v>276.2277271747589</v>
       </c>
       <c r="D6" t="n">
-        <v>6.789999961853027</v>
+        <v>10.48999977111816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3969700948188179</v>
+        <v>0.3282750898285916</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4210526347160339</v>
+        <v>0.5241379141807556</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2911283373832702</v>
+        <v>0.3843700289726257</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2819237112998962</v>
+        <v>0.375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2782900333404541</v>
+        <v>0.3805601298809051</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1213312149047851</v>
+        <v>0.068963386118412</v>
       </c>
       <c r="K6" t="n">
-        <v>63.04998540878296</v>
+        <v>21.93883776664734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1503885825475057</v>
+        <v>0.0652854760487874</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2328549067179362</v>
+        <v>0.1211538235346476</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2696492989857991</v>
+        <v>0.1271576960881551</v>
       </c>
       <c r="O6" t="n">
-        <v>4.511657476425171</v>
+        <v>1.958564281463623</v>
       </c>
       <c r="P6" t="n">
-        <v>6.985647201538086</v>
+        <v>3.634614706039429</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.089478969573975</v>
+        <v>3.814730882644653</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-062442</t>
+          <t>20250730-094041</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7538,53 +7538,53 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>225.3679931163788</v>
+        <v>271.9194204807281</v>
       </c>
       <c r="D2" t="n">
-        <v>1.769999980926514</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2224942251588359</v>
+        <v>0.3069997655622887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5641025900840759</v>
+        <v>0.587699294090271</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4150627553462982</v>
+        <v>0.4242928326129913</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4059652090072632</v>
+        <v>0.4328486025333404</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4317789375782013</v>
+        <v>0.4370629489421844</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1225258335471153</v>
+        <v>0.0910556986927986</v>
       </c>
       <c r="K2" t="n">
-        <v>20.05878329277039</v>
+        <v>42.39968919754028</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1067687511444091</v>
+        <v>0.08255782127380371</v>
       </c>
       <c r="M2" t="n">
-        <v>0.130961807568868</v>
+        <v>0.2013741413752238</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1465344826380411</v>
+        <v>0.1876835743586222</v>
       </c>
       <c r="O2" t="n">
-        <v>3.203062534332275</v>
+        <v>2.476734638214112</v>
       </c>
       <c r="P2" t="n">
-        <v>3.92885422706604</v>
+        <v>6.041224241256714</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.396034479141235</v>
+        <v>5.630507230758667</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-185820</t>
+          <t>20250731-021213</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>136.119341135025</v>
+        <v>206.2031266689301</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2217803233760898</v>
+        <v>0.3061899773279826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5550458431243896</v>
+        <v>0.6714285612106323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3609375059604645</v>
+        <v>0.4593070149421692</v>
       </c>
       <c r="H3" t="n">
-        <v>0.359143316745758</v>
+        <v>0.4475770890712738</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3494486808776855</v>
+        <v>0.4569983184337616</v>
       </c>
       <c r="J3" t="n">
-        <v>0.131007045507431</v>
+        <v>0.0967734977602958</v>
       </c>
       <c r="K3" t="n">
-        <v>20.71849203109741</v>
+        <v>42.59735774993896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1197884480158488</v>
+        <v>0.0928366502126058</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1395409107208252</v>
+        <v>0.2188313166300455</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1434689283370971</v>
+        <v>0.2105691830317179</v>
       </c>
       <c r="O3" t="n">
-        <v>3.593653440475464</v>
+        <v>2.785099506378174</v>
       </c>
       <c r="P3" t="n">
-        <v>4.186227321624756</v>
+        <v>6.564939498901367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.304067850112915</v>
+        <v>6.317075490951538</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-190315</t>
+          <t>20250731-021825</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>261.2648606300354</v>
+        <v>175.3382663726807</v>
       </c>
       <c r="D4" t="n">
-        <v>1.769999980926514</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2219430006068685</v>
+        <v>0.3045667845105368</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5641025900840759</v>
+        <v>0.5054348111152649</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3957307040691376</v>
+        <v>0.4270916283130646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4032114148139953</v>
+        <v>0.4255691766738891</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3720508217811584</v>
+        <v>0.4232142865657806</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1132435351610183</v>
+        <v>0.09384585916995999</v>
       </c>
       <c r="K4" t="n">
-        <v>14.75357842445374</v>
+        <v>42.02279949188232</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1169081846872965</v>
+        <v>0.09886984825134271</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1442710717519124</v>
+        <v>0.2137097835540771</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1420276800791422</v>
+        <v>0.2093647797902425</v>
       </c>
       <c r="O4" t="n">
-        <v>3.507245540618896</v>
+        <v>2.966095447540283</v>
       </c>
       <c r="P4" t="n">
-        <v>4.328132152557373</v>
+        <v>6.411293506622314</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.260830402374268</v>
+        <v>6.280943393707275</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-190641</t>
+          <t>20250731-022324</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>278.031702041626</v>
+        <v>187.0074779987335</v>
       </c>
       <c r="D5" t="n">
-        <v>1.730000019073486</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2218253491370658</v>
+        <v>0.3051270673524088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5950782895088196</v>
+        <v>0.6682134866714478</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3962425291538238</v>
+        <v>0.4616666734218597</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4074373543262481</v>
+        <v>0.449999988079071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2274052500724792</v>
+        <v>0.4602368772029876</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1193751469254493</v>
+        <v>0.1026064530014991</v>
       </c>
       <c r="K5" t="n">
-        <v>20.81890630722046</v>
+        <v>41.99710273742676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1085076252619425</v>
+        <v>0.0895036379496256</v>
       </c>
       <c r="M5" t="n">
-        <v>0.138896910349528</v>
+        <v>0.2046003580093383</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1413472811381022</v>
+        <v>0.1867907047271728</v>
       </c>
       <c r="O5" t="n">
-        <v>3.255228757858276</v>
+        <v>2.685109138488769</v>
       </c>
       <c r="P5" t="n">
-        <v>4.16690731048584</v>
+        <v>6.138010740280151</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.240418434143066</v>
+        <v>5.603721141815186</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-191206</t>
+          <t>20250731-022750</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>171.5487785339355</v>
+        <v>183.9974837303162</v>
       </c>
       <c r="D6" t="n">
-        <v>1.720000028610229</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2230090560515721</v>
+        <v>0.3047515256191367</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6026200652122498</v>
+        <v>0.5300207138061523</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4256816208362579</v>
+        <v>0.4319526553153991</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4098504781723022</v>
+        <v>0.4275303781032562</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3985952734947204</v>
+        <v>0.4295942783355713</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1136378571391105</v>
+        <v>0.0855419933795929</v>
       </c>
       <c r="K6" t="n">
-        <v>20.78219699859619</v>
+        <v>36.87540292739868</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1124977668126424</v>
+        <v>0.0952265342076619</v>
       </c>
       <c r="M6" t="n">
-        <v>0.127316935857137</v>
+        <v>0.2326999266942342</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1464159488677978</v>
+        <v>0.189913813273112</v>
       </c>
       <c r="O6" t="n">
-        <v>3.374933004379272</v>
+        <v>2.856796026229858</v>
       </c>
       <c r="P6" t="n">
-        <v>3.819508075714111</v>
+        <v>6.980997800827026</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.392478466033936</v>
+        <v>5.697414398193359</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-191754</t>
+          <t>20250731-023238</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>150.2156126499176</v>
+        <v>124.4577260017395</v>
       </c>
       <c r="D2" t="n">
-        <v>5.449999809265137</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3260905380342521</v>
+        <v>0.2099611111103542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5165876746177673</v>
+        <v>0.6265060305595398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2835011482238769</v>
+        <v>0.4057480990886688</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2765055000782013</v>
+        <v>0.4040574729442596</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2830188572406769</v>
+        <v>0.4159592390060425</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0850928276777267</v>
+        <v>0.1066460311412811</v>
       </c>
       <c r="K2" t="n">
-        <v>22.25268602371216</v>
+        <v>29.18390607833862</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0757087469100952</v>
+        <v>0.077248469988505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.118868335088094</v>
+        <v>0.151334015528361</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1231619834899902</v>
+        <v>0.1957474152247111</v>
       </c>
       <c r="O2" t="n">
-        <v>2.271262407302856</v>
+        <v>2.317454099655152</v>
       </c>
       <c r="P2" t="n">
-        <v>3.566050052642822</v>
+        <v>4.54002046585083</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.694859504699707</v>
+        <v>5.872422456741333</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-084449</t>
+          <t>20250627-162249</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>194.2934136390686</v>
+        <v>84.61009502410889</v>
       </c>
       <c r="D3" t="n">
-        <v>5.449999809265137</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3218178130797486</v>
+        <v>0.2029099772835886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5213032364845276</v>
+        <v>0.5450901985168457</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3340891897678375</v>
+        <v>0.3907666802406311</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3354430496692657</v>
+        <v>0.393415629863739</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3380503058433532</v>
+        <v>0.3939899802207947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.083680123090744</v>
+        <v>0.0994007140398025</v>
       </c>
       <c r="K3" t="n">
-        <v>22.07885527610779</v>
+        <v>29.46430850028992</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07257988452911369</v>
+        <v>0.0757128636042277</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1226659297943115</v>
+        <v>0.1496650218963623</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1259541670481364</v>
+        <v>0.1941637198130289</v>
       </c>
       <c r="O3" t="n">
-        <v>2.177396535873413</v>
+        <v>2.271385908126831</v>
       </c>
       <c r="P3" t="n">
-        <v>3.679977893829346</v>
+        <v>4.489950656890869</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.778625011444092</v>
+        <v>5.824911594390869</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-084827</t>
+          <t>20250627-162606</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>290.0046889781952</v>
+        <v>91.76186800003052</v>
       </c>
       <c r="D4" t="n">
-        <v>5.480000019073486</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3142825700704333</v>
+        <v>0.2024087623712864</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4987013041973114</v>
+        <v>0.5902438759803772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3657407462596893</v>
+        <v>0.3790322542190552</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3360143005847931</v>
+        <v>0.3784692883491516</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3327305614948272</v>
+        <v>0.3696202635765075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0887447670102119</v>
+        <v>0.097963809967041</v>
       </c>
       <c r="K4" t="n">
-        <v>22.016841173172</v>
+        <v>29.36896204948425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0701960245768229</v>
+        <v>0.07467085520426429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1202012618382771</v>
+        <v>0.1487170775731404</v>
       </c>
       <c r="N4" t="n">
-        <v>0.129391344388326</v>
+        <v>0.1735356092453003</v>
       </c>
       <c r="O4" t="n">
-        <v>2.105880737304688</v>
+        <v>2.24012565612793</v>
       </c>
       <c r="P4" t="n">
-        <v>3.606037855148315</v>
+        <v>4.461512327194214</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88174033164978</v>
+        <v>5.206068277359009</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-085250</t>
+          <t>20250627-162844</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>221.2956192493439</v>
+        <v>86.65130639076233</v>
       </c>
       <c r="D5" t="n">
-        <v>5.429999828338623</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3124083755891534</v>
+        <v>0.2146787369667097</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5033112764358521</v>
+        <v>0.6091127395629883</v>
       </c>
       <c r="G5" t="n">
-        <v>0.358208954334259</v>
+        <v>0.3996641337871551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3538083434104919</v>
+        <v>0.3935309946537018</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3592622280120849</v>
+        <v>0.3871559500694275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07970760762691489</v>
+        <v>0.08841155469417571</v>
       </c>
       <c r="K5" t="n">
-        <v>22.16102766990662</v>
+        <v>29.27169227600098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0724782864252726</v>
+        <v>0.0735185702641805</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1232327381769816</v>
+        <v>0.1473366419474283</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1278765678405761</v>
+        <v>0.1715156952540079</v>
       </c>
       <c r="O5" t="n">
-        <v>2.174348592758179</v>
+        <v>2.205557107925415</v>
       </c>
       <c r="P5" t="n">
-        <v>3.696982145309448</v>
+        <v>4.420099258422852</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.836297035217285</v>
+        <v>5.145470857620239</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-085848</t>
+          <t>20250627-163138</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>343.7080183029175</v>
+        <v>140.0147500038147</v>
       </c>
       <c r="D6" t="n">
-        <v>5.449999809265137</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.334828087557917</v>
+        <v>0.2115021398369695</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5626477599143982</v>
+        <v>0.6430379748344421</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3633633553981781</v>
+        <v>0.4233226776123047</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3595317602157593</v>
+        <v>0.3996478915214538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3602378964424133</v>
+        <v>0.3946902751922607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0845692008733749</v>
+        <v>0.1002362444996833</v>
       </c>
       <c r="K6" t="n">
-        <v>22.02216124534607</v>
+        <v>28.92077803611756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0690097570419311</v>
+        <v>0.0731848319371541</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1229564984639485</v>
+        <v>0.1508809010187785</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1259994188944498</v>
+        <v>0.2088205893834432</v>
       </c>
       <c r="O6" t="n">
-        <v>2.070292711257935</v>
+        <v>2.195544958114624</v>
       </c>
       <c r="P6" t="n">
-        <v>3.688694953918457</v>
+        <v>4.526427030563354</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.779982566833496</v>
+        <v>6.264617681503296</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-090337</t>
+          <t>20250627-163427</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>163.1326968669891</v>
+        <v>225.3679931163788</v>
       </c>
       <c r="D2" t="n">
-        <v>7.440000057220459</v>
+        <v>1.769999980926514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2264845437967955</v>
+        <v>0.2224942251588359</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5528090000152588</v>
+        <v>0.5641025900840759</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3827893137931824</v>
+        <v>0.4150627553462982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3968368172645569</v>
+        <v>0.4059652090072632</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3875969052314758</v>
+        <v>0.4317789375782013</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0811535492539405</v>
+        <v>0.1225258335471153</v>
       </c>
       <c r="K2" t="n">
-        <v>37.16039228439331</v>
+        <v>20.05878329277039</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1183988730112711</v>
+        <v>0.1067687511444091</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2212436914443969</v>
+        <v>0.130961807568868</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2098087867101033</v>
+        <v>0.1465344826380411</v>
       </c>
       <c r="O2" t="n">
-        <v>3.551966190338135</v>
+        <v>3.203062534332275</v>
       </c>
       <c r="P2" t="n">
-        <v>6.637310743331909</v>
+        <v>3.92885422706604</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.294263601303101</v>
+        <v>4.396034479141235</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-105226</t>
+          <t>20250701-185820</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>223.9305365085602</v>
+        <v>136.119341135025</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2257847898884823</v>
+        <v>0.2217803233760898</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5835294127464294</v>
+        <v>0.5550458431243896</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4271999895572662</v>
+        <v>0.3609375059604645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4184100329875946</v>
+        <v>0.359143316745758</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4097646176815033</v>
+        <v>0.3494486808776855</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08065438270568839</v>
+        <v>0.131007045507431</v>
       </c>
       <c r="K3" t="n">
-        <v>42.34947299957275</v>
+        <v>20.71849203109741</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1048675934473673</v>
+        <v>0.1197884480158488</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2009020566940307</v>
+        <v>0.1395409107208252</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1871054808298747</v>
+        <v>0.1434689283370971</v>
       </c>
       <c r="O3" t="n">
-        <v>3.146027803421021</v>
+        <v>3.593653440475464</v>
       </c>
       <c r="P3" t="n">
-        <v>6.027061700820923</v>
+        <v>4.186227321624756</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.61316442489624</v>
+        <v>4.304067850112915</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-105638</t>
+          <t>20250701-190315</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>84.74034094810486</v>
+        <v>261.2648606300354</v>
       </c>
       <c r="D4" t="n">
-        <v>7.420000076293945</v>
+        <v>1.769999980926514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2273105242422648</v>
+        <v>0.2219430006068685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5300353169441223</v>
+        <v>0.5641025900840759</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3869499266147613</v>
+        <v>0.3957307040691376</v>
       </c>
       <c r="H4" t="n">
-        <v>0.391882449388504</v>
+        <v>0.4032114148139953</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3853073418140411</v>
+        <v>0.3720508217811584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07406088709831229</v>
+        <v>0.1132435351610183</v>
       </c>
       <c r="K4" t="n">
-        <v>36.53185939788818</v>
+        <v>14.75357842445374</v>
       </c>
       <c r="L4" t="n">
-        <v>0.115849757194519</v>
+        <v>0.1169081846872965</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2023777643839518</v>
+        <v>0.1442710717519124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1923651377360026</v>
+        <v>0.1420276800791422</v>
       </c>
       <c r="O4" t="n">
-        <v>3.475492715835572</v>
+        <v>3.507245540618896</v>
       </c>
       <c r="P4" t="n">
-        <v>6.071332931518555</v>
+        <v>4.328132152557373</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.770954132080078</v>
+        <v>4.260830402374268</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-110204</t>
+          <t>20250701-190641</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>157.2109234333038</v>
+        <v>278.031702041626</v>
       </c>
       <c r="D5" t="n">
-        <v>7.440000057220459</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2271623658155327</v>
+        <v>0.2218253491370658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6056910753250122</v>
+        <v>0.5950782895088196</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4273635745048523</v>
+        <v>0.3962425291538238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4264264404773712</v>
+        <v>0.4074373543262481</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4139610528945923</v>
+        <v>0.2274052500724792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0933835357427597</v>
+        <v>0.1193751469254493</v>
       </c>
       <c r="K5" t="n">
-        <v>42.37400960922241</v>
+        <v>20.81890630722046</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1207546790440877</v>
+        <v>0.1085076252619425</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2060715039571126</v>
+        <v>0.138896910349528</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1912790536880493</v>
+        <v>0.1413472811381022</v>
       </c>
       <c r="O5" t="n">
-        <v>3.622640371322632</v>
+        <v>3.255228757858276</v>
       </c>
       <c r="P5" t="n">
-        <v>6.182145118713379</v>
+        <v>4.16690731048584</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.73837161064148</v>
+        <v>4.240418434143066</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-110512</t>
+          <t>20250701-191206</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C6" t="n">
-        <v>140.6683385372162</v>
+        <v>171.5487785339355</v>
       </c>
       <c r="D6" t="n">
-        <v>7.46999979019165</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2237928171279066</v>
+        <v>0.2230090560515721</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5373134613037109</v>
+        <v>0.6026200652122498</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4122516512870788</v>
+        <v>0.4256816208362579</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4027072787284851</v>
+        <v>0.4098504781723022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.398333340883255</v>
+        <v>0.3985952734947204</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0816067531704902</v>
+        <v>0.1136378571391105</v>
       </c>
       <c r="K6" t="n">
-        <v>37.29435873031616</v>
+        <v>20.78219699859619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1077330271402994</v>
+        <v>0.1124977668126424</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1992581685384114</v>
+        <v>0.127316935857137</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1824308077494303</v>
+        <v>0.1464159488677978</v>
       </c>
       <c r="O6" t="n">
-        <v>3.231990814208984</v>
+        <v>3.374933004379272</v>
       </c>
       <c r="P6" t="n">
-        <v>5.977745056152344</v>
+        <v>3.819508075714111</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.47292423248291</v>
+        <v>4.392478466033936</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-110932</t>
+          <t>20250701-191754</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
